--- a/results/test/vicon_MQI_wrists_head_normByShoulders.xlsx
+++ b/results/test/vicon_MQI_wrists_head_normByShoulders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,190 +661,285 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/SEMID01.csv</t>
+          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/SEATEDD08.csv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SEMID01.csv</t>
+          <t>SEATEDD08.csv</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8668.166076665064</v>
+        <v>12391.59599663952</v>
       </c>
       <c r="D3" t="n">
         <v>17999</v>
       </c>
       <c r="E3" t="n">
-        <v>6035.964257009496</v>
+        <v>7032.863643195496</v>
       </c>
       <c r="F3" t="n">
         <v>17999</v>
       </c>
       <c r="G3" t="n">
-        <v>14704.13033367456</v>
+        <v>19424.45963983501</v>
       </c>
       <c r="H3" t="n">
-        <v>13942.42811964512</v>
+        <v>8247.951476681654</v>
       </c>
       <c r="I3" t="n">
         <v>17999</v>
       </c>
       <c r="J3" t="n">
-        <v>14935.84173361575</v>
+        <v>7904.140424515247</v>
       </c>
       <c r="K3" t="n">
         <v>17999</v>
       </c>
       <c r="L3" t="n">
-        <v>28878.26985326087</v>
+        <v>16152.0919011969</v>
       </c>
       <c r="M3" t="n">
-        <v>7473.133557300522</v>
+        <v>10612.73232351746</v>
       </c>
       <c r="N3" t="n">
         <v>17999</v>
       </c>
       <c r="O3" t="n">
-        <v>8656.559834993594</v>
+        <v>19406.99964315136</v>
       </c>
       <c r="P3" t="n">
         <v>17999</v>
       </c>
       <c r="Q3" t="n">
-        <v>16129.69339229412</v>
+        <v>30019.73196666882</v>
       </c>
       <c r="R3" t="n">
-        <v>8852.532002180582</v>
+        <v>10175.95648137923</v>
       </c>
       <c r="S3" t="n">
         <v>17999</v>
       </c>
       <c r="T3" t="n">
-        <v>9113.59736809379</v>
+        <v>9455.445587950535</v>
       </c>
       <c r="U3" t="n">
         <v>17999</v>
       </c>
       <c r="V3" t="n">
-        <v>17966.12937027437</v>
+        <v>19631.40206932976</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SEMID01</t>
+          <t>SEATEDD08</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>284.5477680640457</v>
+        <v>327.8591878040019</v>
       </c>
       <c r="Y3" t="n">
-        <v>336.0979522274564</v>
+        <v>442.0891707732675</v>
       </c>
       <c r="Z3" t="n">
-        <v>51.67543725159344</v>
+        <v>59.24634831782473</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.99104929201785</v>
+        <v>67.90424636315039</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.4883021214244</v>
+        <v>49.26533250260112</v>
       </c>
       <c r="AC3" t="n">
-        <v>53.45503967282633</v>
+        <v>44.40597817628525</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/SEMID01.csv</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SEMID01.csv</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8668.166076665064</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6035.964257009496</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14704.13033367456</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13942.42811964512</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14935.84173361575</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="L4" t="n">
+        <v>28878.26985326087</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7473.133557300522</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8656.559834993594</v>
+      </c>
+      <c r="P4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>16129.69339229412</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8852.532002180582</v>
+      </c>
+      <c r="S4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9113.59736809379</v>
+      </c>
+      <c r="U4" t="n">
+        <v>17999</v>
+      </c>
+      <c r="V4" t="n">
+        <v>17966.12937027437</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SEMID01</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>284.5477680640457</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>336.0979522274564</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>51.67543725159344</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>47.99104929201785</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>101.4883021214244</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>53.45503967282633</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>/Users/matysprecloux/Desktop/Master IEAP/Code MOTTET/Defense /SYNCOGESTM2/data/test/vicon_csv/STANDINGD01.csv</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>STANDINGD01.csv</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>21176.21191864776</v>
       </c>
-      <c r="D4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="E5" t="n">
         <v>18263.69262989775</v>
       </c>
-      <c r="F4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="G5" t="n">
         <v>39439.90454854551</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>15582.85548083792</v>
       </c>
-      <c r="I4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="J5" t="n">
         <v>17012.96076622347</v>
       </c>
-      <c r="K4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="K5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="L5" t="n">
         <v>32595.81624706139</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5" t="n">
         <v>23389.33042514446</v>
       </c>
-      <c r="N4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="N5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="O5" t="n">
         <v>22248.21312258438</v>
       </c>
-      <c r="P4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="P5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="Q5" t="n">
         <v>45637.54354772884</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>13910.02384810666</v>
       </c>
-      <c r="S4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="S5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="T5" t="n">
         <v>13998.87502220762</v>
       </c>
-      <c r="U4" t="n">
-        <v>17999</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="U5" t="n">
+        <v>17999</v>
+      </c>
+      <c r="V5" t="n">
         <v>27908.89887031429</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>STANDINGD01</t>
         </is>
       </c>
-      <c r="X4" t="n">
+      <c r="X5" t="n">
         <v>290.3214874392707</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y5" t="n">
         <v>345.8507837970011</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z5" t="n">
         <v>135.8490716495641</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA5" t="n">
         <v>131.9573228855715</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB5" t="n">
         <v>112.2749009539976</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC5" t="n">
         <v>80.69635859693631</v>
       </c>
     </row>
